--- a/NURBS IDX11 PYTHON ANALYSIS/8_4_2026_Redo_front/15gps/redo_front_15gps_summary.xlsx
+++ b/NURBS IDX11 PYTHON ANALYSIS/8_4_2026_Redo_front/15gps/redo_front_15gps_summary.xlsx
@@ -384,10 +384,10 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>247.9420662470201</v>
+        <v>248.2541260715633</v>
       </c>
       <c r="C3">
-        <v>23.5612009976136</v>
+        <v>23.56858304551885</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -406,10 +406,10 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>433.351826473298</v>
+        <v>433.3851235729551</v>
       </c>
       <c r="C5">
-        <v>23.41105088673355</v>
+        <v>23.41140021852875</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -417,10 +417,10 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>481.6215375352495</v>
+        <v>481.7457790667899</v>
       </c>
       <c r="C6">
-        <v>23.39675980107645</v>
+        <v>23.39793098181051</v>
       </c>
     </row>
     <row r="7" spans="1:3">
